--- a/AAII_Financials/Yearly/AWATY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/AWATY_YR_FIN.xlsx
@@ -302,7 +302,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -344,7 +344,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -653,135 +653,147 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:L102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44651</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44286</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43921</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43555</v>
       </c>
-      <c r="K7" s="2"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L7" s="2"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>7184900</v>
+        <v>6709200</v>
       </c>
       <c r="E8" s="3">
-        <v>6773600</v>
+        <v>6765200</v>
       </c>
       <c r="F8" s="3">
-        <v>7559500</v>
+        <v>6389000</v>
       </c>
       <c r="G8" s="3">
-        <v>7318100</v>
+        <v>7176400</v>
       </c>
       <c r="H8" s="3">
-        <v>7293300</v>
+        <v>6972900</v>
       </c>
       <c r="I8" s="3">
+        <v>6937000</v>
+      </c>
+      <c r="J8" s="3">
         <v>7519200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>7233000</v>
       </c>
-      <c r="K8" s="3"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L8" s="3"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>5638800</v>
+        <v>5197900</v>
       </c>
       <c r="E9" s="3">
-        <v>5317300</v>
+        <v>5270900</v>
       </c>
       <c r="F9" s="3">
-        <v>6054400</v>
+        <v>4957200</v>
       </c>
       <c r="G9" s="3">
-        <v>5678400</v>
+        <v>5946800</v>
       </c>
       <c r="H9" s="3">
-        <v>5657700</v>
+        <v>5341400</v>
       </c>
       <c r="I9" s="3">
+        <v>5307600</v>
+      </c>
+      <c r="J9" s="3">
         <v>5840600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>5696500</v>
       </c>
-      <c r="K9" s="3"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>1546100</v>
+        <v>1511300</v>
       </c>
       <c r="E10" s="3">
-        <v>1456300</v>
+        <v>1494300</v>
       </c>
       <c r="F10" s="3">
-        <v>1505100</v>
+        <v>1431900</v>
       </c>
       <c r="G10" s="3">
-        <v>1639700</v>
+        <v>1229600</v>
       </c>
       <c r="H10" s="3">
-        <v>1635600</v>
+        <v>1631600</v>
       </c>
       <c r="I10" s="3">
+        <v>1629400</v>
+      </c>
+      <c r="J10" s="3">
         <v>1678600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1536500</v>
       </c>
-      <c r="K10" s="3"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="3"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -793,35 +805,39 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>33300</v>
+        <v>32100</v>
       </c>
       <c r="E12" s="3">
-        <v>40800</v>
+        <v>33600</v>
       </c>
       <c r="F12" s="3">
-        <v>41000</v>
+        <v>42000</v>
       </c>
       <c r="G12" s="3">
-        <v>44000</v>
+        <v>44400</v>
       </c>
       <c r="H12" s="3">
-        <v>36000</v>
+        <v>44800</v>
       </c>
       <c r="I12" s="3">
+        <v>37000</v>
+      </c>
+      <c r="J12" s="3">
         <v>31800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>25800</v>
       </c>
-      <c r="K12" s="3"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -846,63 +862,72 @@
       <c r="J13" s="3">
         <v>0</v>
       </c>
-      <c r="K13" s="3"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K13" s="3">
+        <v>0</v>
+      </c>
+      <c r="L13" s="3"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>-24600</v>
+        <v>507500</v>
       </c>
       <c r="E14" s="3">
-        <v>-2500</v>
+        <v>-1200</v>
       </c>
       <c r="F14" s="3">
-        <v>-24600</v>
+        <v>9900</v>
       </c>
       <c r="G14" s="3">
-        <v>1800</v>
+        <v>-16100</v>
       </c>
       <c r="H14" s="3">
-        <v>2500</v>
+        <v>2100</v>
       </c>
       <c r="I14" s="3">
+        <v>11000</v>
+      </c>
+      <c r="J14" s="3">
         <v>-14400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>64400</v>
       </c>
-      <c r="K14" s="3"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="3"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>117000</v>
+        <v>140600</v>
       </c>
       <c r="E15" s="3">
-        <v>110100</v>
+        <v>120500</v>
       </c>
       <c r="F15" s="3">
-        <v>115600</v>
+        <v>111900</v>
       </c>
       <c r="G15" s="3">
-        <v>116600</v>
+        <v>116300</v>
       </c>
       <c r="H15" s="3">
-        <v>126300</v>
+        <v>113900</v>
       </c>
       <c r="I15" s="3">
+        <v>120500</v>
+      </c>
+      <c r="J15" s="3">
         <v>111200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>84500</v>
       </c>
-      <c r="K15" s="3"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="3"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -911,62 +936,69 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>6741400</v>
+        <v>6466600</v>
       </c>
       <c r="E17" s="3">
-        <v>6346800</v>
+        <v>6388900</v>
       </c>
       <c r="F17" s="3">
-        <v>7153100</v>
+        <v>6011700</v>
       </c>
       <c r="G17" s="3">
-        <v>6813600</v>
+        <v>7051700</v>
       </c>
       <c r="H17" s="3">
-        <v>6864200</v>
+        <v>6491100</v>
       </c>
       <c r="I17" s="3">
+        <v>6528200</v>
+      </c>
+      <c r="J17" s="3">
         <v>7084200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>6839800</v>
       </c>
-      <c r="K17" s="3"/>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L17" s="3"/>
+    </row>
+    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>443600</v>
+        <v>242600</v>
       </c>
       <c r="E18" s="3">
-        <v>426800</v>
+        <v>376300</v>
       </c>
       <c r="F18" s="3">
-        <v>406400</v>
+        <v>377400</v>
       </c>
       <c r="G18" s="3">
-        <v>504500</v>
+        <v>124800</v>
       </c>
       <c r="H18" s="3">
-        <v>429100</v>
+        <v>481900</v>
       </c>
       <c r="I18" s="3">
+        <v>408800</v>
+      </c>
+      <c r="J18" s="3">
         <v>435100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>393300</v>
       </c>
-      <c r="K18" s="3"/>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L18" s="3"/>
+    </row>
+    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -978,143 +1010,159 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>-31900</v>
+        <v>37800</v>
       </c>
       <c r="E20" s="3">
-        <v>-20400</v>
+        <v>-43700</v>
       </c>
       <c r="F20" s="3">
-        <v>-32000</v>
+        <v>-24600</v>
       </c>
       <c r="G20" s="3">
-        <v>-28800</v>
+        <v>-26800</v>
       </c>
       <c r="H20" s="3">
-        <v>-28100</v>
+        <v>-37500</v>
       </c>
       <c r="I20" s="3">
+        <v>-31000</v>
+      </c>
+      <c r="J20" s="3">
         <v>-15400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-32800</v>
       </c>
-      <c r="K20" s="3"/>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L20" s="3"/>
+    </row>
+    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>592500</v>
+        <v>345400</v>
       </c>
       <c r="E21" s="3">
-        <v>557300</v>
+        <v>540500</v>
       </c>
       <c r="F21" s="3">
-        <v>554000</v>
+        <v>513900</v>
       </c>
       <c r="G21" s="3">
-        <v>649900</v>
+        <v>267900</v>
       </c>
       <c r="H21" s="3">
-        <v>583400</v>
+        <v>633200</v>
       </c>
       <c r="I21" s="3">
+        <v>560300</v>
+      </c>
+      <c r="J21" s="3">
         <v>561700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>510600</v>
       </c>
-      <c r="K21" s="3"/>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3"/>
+    </row>
+    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
-        <v>25900</v>
+        <v>36700</v>
       </c>
       <c r="E22" s="3">
-        <v>21300</v>
+        <v>34600</v>
       </c>
       <c r="F22" s="3">
-        <v>15000</v>
+        <v>27900</v>
       </c>
       <c r="G22" s="3">
-        <v>12200</v>
+        <v>22100</v>
       </c>
       <c r="H22" s="3">
-        <v>14900</v>
+        <v>20100</v>
       </c>
       <c r="I22" s="3">
+        <v>23800</v>
+      </c>
+      <c r="J22" s="3">
         <v>13500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>13000</v>
       </c>
-      <c r="K22" s="3"/>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="3"/>
+    </row>
+    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
-        <v>494000</v>
+        <v>-323600</v>
       </c>
       <c r="E23" s="3">
-        <v>441000</v>
+        <v>406500</v>
       </c>
       <c r="F23" s="3">
-        <v>458700</v>
+        <v>376800</v>
       </c>
       <c r="G23" s="3">
-        <v>528900</v>
+        <v>156300</v>
       </c>
       <c r="H23" s="3">
-        <v>448900</v>
+        <v>506600</v>
       </c>
       <c r="I23" s="3">
+        <v>414100</v>
+      </c>
+      <c r="J23" s="3">
         <v>463100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>359500</v>
       </c>
-      <c r="K23" s="3"/>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L23" s="3"/>
+    </row>
+    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
-        <v>157400</v>
+        <v>93300</v>
       </c>
       <c r="E24" s="3">
-        <v>136000</v>
+        <v>146200</v>
       </c>
       <c r="F24" s="3">
-        <v>135600</v>
+        <v>130300</v>
       </c>
       <c r="G24" s="3">
-        <v>146800</v>
+        <v>71700</v>
       </c>
       <c r="H24" s="3">
-        <v>174400</v>
+        <v>139100</v>
       </c>
       <c r="I24" s="3">
+        <v>173700</v>
+      </c>
+      <c r="J24" s="3">
         <v>149500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>106200</v>
       </c>
-      <c r="K24" s="3"/>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3"/>
+    </row>
+    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1139,63 +1187,72 @@
       <c r="J25" s="3">
         <v>0</v>
       </c>
-      <c r="K25" s="3"/>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K25" s="3">
+        <v>0</v>
+      </c>
+      <c r="L25" s="3"/>
+    </row>
+    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
-        <v>336600</v>
+        <v>-416800</v>
       </c>
       <c r="E26" s="3">
-        <v>305100</v>
+        <v>260200</v>
       </c>
       <c r="F26" s="3">
-        <v>323100</v>
+        <v>246500</v>
       </c>
       <c r="G26" s="3">
-        <v>382100</v>
+        <v>84600</v>
       </c>
       <c r="H26" s="3">
-        <v>274500</v>
+        <v>367500</v>
       </c>
       <c r="I26" s="3">
+        <v>240400</v>
+      </c>
+      <c r="J26" s="3">
         <v>313600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>253300</v>
       </c>
-      <c r="K26" s="3"/>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L26" s="3"/>
+    </row>
+    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>327700</v>
+        <v>-402200</v>
       </c>
       <c r="E27" s="3">
-        <v>293300</v>
+        <v>266600</v>
       </c>
       <c r="F27" s="3">
-        <v>301900</v>
+        <v>242200</v>
       </c>
       <c r="G27" s="3">
-        <v>355900</v>
+        <v>69700</v>
       </c>
       <c r="H27" s="3">
-        <v>247400</v>
+        <v>343100</v>
       </c>
       <c r="I27" s="3">
+        <v>215700</v>
+      </c>
+      <c r="J27" s="3">
         <v>282800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>238900</v>
       </c>
-      <c r="K27" s="3"/>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L27" s="3"/>
+    </row>
+    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1220,36 +1277,42 @@
       <c r="J28" s="3">
         <v>0</v>
       </c>
-      <c r="K28" s="3"/>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K28" s="3">
+        <v>0</v>
+      </c>
+      <c r="L28" s="3"/>
+    </row>
+    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D29" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E29" s="3">
         <v>-100</v>
       </c>
       <c r="F29" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G29" s="3">
         <v>-2300</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>-1200</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>500</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-2000</v>
       </c>
-      <c r="J29" s="3">
-        <v>0</v>
-      </c>
-      <c r="K29" s="3"/>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3"/>
+    </row>
+    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1274,9 +1337,12 @@
       <c r="J30" s="3">
         <v>0</v>
       </c>
-      <c r="K30" s="3"/>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K30" s="3">
+        <v>0</v>
+      </c>
+      <c r="L30" s="3"/>
+    </row>
+    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -1301,63 +1367,72 @@
       <c r="J31" s="3">
         <v>0</v>
       </c>
-      <c r="K31" s="3"/>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K31" s="3">
+        <v>0</v>
+      </c>
+      <c r="L31" s="3"/>
+    </row>
+    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>31900</v>
+        <v>-37800</v>
       </c>
       <c r="E32" s="3">
-        <v>20400</v>
+        <v>43700</v>
       </c>
       <c r="F32" s="3">
-        <v>32000</v>
+        <v>24600</v>
       </c>
       <c r="G32" s="3">
-        <v>28800</v>
+        <v>26800</v>
       </c>
       <c r="H32" s="3">
-        <v>28100</v>
+        <v>37500</v>
       </c>
       <c r="I32" s="3">
+        <v>31000</v>
+      </c>
+      <c r="J32" s="3">
         <v>15400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>32800</v>
       </c>
-      <c r="K32" s="3"/>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L32" s="3"/>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
-        <v>327700</v>
+        <v>-402200</v>
       </c>
       <c r="E33" s="3">
-        <v>293300</v>
+        <v>266600</v>
       </c>
       <c r="F33" s="3">
-        <v>301900</v>
+        <v>242200</v>
       </c>
       <c r="G33" s="3">
-        <v>355900</v>
+        <v>69700</v>
       </c>
       <c r="H33" s="3">
-        <v>247400</v>
+        <v>343100</v>
       </c>
       <c r="I33" s="3">
+        <v>215700</v>
+      </c>
+      <c r="J33" s="3">
         <v>282800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>238900</v>
       </c>
-      <c r="K33" s="3"/>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L33" s="3"/>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -1382,68 +1457,77 @@
       <c r="J34" s="3">
         <v>0</v>
       </c>
-      <c r="K34" s="3"/>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K34" s="3">
+        <v>0</v>
+      </c>
+      <c r="L34" s="3"/>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
-        <v>327700</v>
+        <v>-402200</v>
       </c>
       <c r="E35" s="3">
-        <v>293300</v>
+        <v>266600</v>
       </c>
       <c r="F35" s="3">
-        <v>301900</v>
+        <v>242200</v>
       </c>
       <c r="G35" s="3">
-        <v>355900</v>
+        <v>69700</v>
       </c>
       <c r="H35" s="3">
-        <v>247400</v>
+        <v>343100</v>
       </c>
       <c r="I35" s="3">
+        <v>215700</v>
+      </c>
+      <c r="J35" s="3">
         <v>282800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>238900</v>
       </c>
-      <c r="K35" s="3"/>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L35" s="3"/>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44651</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44286</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43921</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43555</v>
       </c>
-      <c r="K38" s="2"/>
-    </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L38" s="2"/>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -1455,8 +1539,9 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -1468,35 +1553,39 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
-        <v>471500</v>
+        <v>548000</v>
       </c>
       <c r="E41" s="3">
-        <v>429600</v>
+        <v>489000</v>
       </c>
       <c r="F41" s="3">
-        <v>496100</v>
+        <v>445900</v>
       </c>
       <c r="G41" s="3">
-        <v>490400</v>
+        <v>531600</v>
       </c>
       <c r="H41" s="3">
-        <v>415800</v>
+        <v>516400</v>
       </c>
       <c r="I41" s="3">
+        <v>453000</v>
+      </c>
+      <c r="J41" s="3">
         <v>389000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>294400</v>
       </c>
-      <c r="K41" s="3"/>
-    </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L41" s="3"/>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
@@ -1521,198 +1610,222 @@
       <c r="J42" s="3">
         <v>0</v>
       </c>
-      <c r="K42" s="3"/>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3"/>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
-        <v>1627100</v>
+        <v>1317700</v>
       </c>
       <c r="E43" s="3">
-        <v>1606900</v>
+        <v>1550200</v>
       </c>
       <c r="F43" s="3">
-        <v>1757100</v>
+        <v>1554500</v>
       </c>
       <c r="G43" s="3">
-        <v>1702300</v>
+        <v>1718900</v>
       </c>
       <c r="H43" s="3">
-        <v>1736900</v>
+        <v>1698600</v>
       </c>
       <c r="I43" s="3">
+        <v>1698300</v>
+      </c>
+      <c r="J43" s="3">
         <v>1769400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1785600</v>
       </c>
-      <c r="K43" s="3"/>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L43" s="3"/>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
-        <v>655900</v>
+        <v>765800</v>
       </c>
       <c r="E44" s="3">
-        <v>612500</v>
+        <v>674500</v>
       </c>
       <c r="F44" s="3">
-        <v>692200</v>
+        <v>627000</v>
       </c>
       <c r="G44" s="3">
-        <v>629200</v>
+        <v>699600</v>
       </c>
       <c r="H44" s="3">
-        <v>611900</v>
+        <v>635100</v>
       </c>
       <c r="I44" s="3">
+        <v>633300</v>
+      </c>
+      <c r="J44" s="3">
         <v>598600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>542800</v>
       </c>
-      <c r="K44" s="3"/>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L44" s="3"/>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
-        <v>294600</v>
+        <v>303200</v>
       </c>
       <c r="E45" s="3">
-        <v>322000</v>
+        <v>241500</v>
       </c>
       <c r="F45" s="3">
-        <v>297900</v>
+        <v>268800</v>
       </c>
       <c r="G45" s="3">
-        <v>281800</v>
+        <v>251400</v>
       </c>
       <c r="H45" s="3">
-        <v>271300</v>
+        <v>221200</v>
       </c>
       <c r="I45" s="3">
+        <v>203800</v>
+      </c>
+      <c r="J45" s="3">
         <v>340200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>132600</v>
       </c>
-      <c r="K45" s="3"/>
-    </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L45" s="3"/>
+    </row>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
-        <v>3049100</v>
+        <v>2934700</v>
       </c>
       <c r="E46" s="3">
-        <v>2971000</v>
+        <v>2955200</v>
       </c>
       <c r="F46" s="3">
-        <v>3243300</v>
+        <v>2896100</v>
       </c>
       <c r="G46" s="3">
-        <v>3103700</v>
+        <v>3201400</v>
       </c>
       <c r="H46" s="3">
-        <v>3035900</v>
+        <v>3071300</v>
       </c>
       <c r="I46" s="3">
+        <v>2988400</v>
+      </c>
+      <c r="J46" s="3">
         <v>3097300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2755400</v>
       </c>
-      <c r="K46" s="3"/>
-    </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L46" s="3"/>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
-        <v>946500</v>
+        <v>956900</v>
       </c>
       <c r="E47" s="3">
-        <v>957400</v>
+        <v>899500</v>
       </c>
       <c r="F47" s="3">
-        <v>881500</v>
+        <v>912600</v>
       </c>
       <c r="G47" s="3">
-        <v>927700</v>
+        <v>823600</v>
       </c>
       <c r="H47" s="3">
-        <v>947600</v>
+        <v>877600</v>
       </c>
       <c r="I47" s="3">
+        <v>916800</v>
+      </c>
+      <c r="J47" s="3">
         <v>887100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>854200</v>
       </c>
-      <c r="K47" s="3"/>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L47" s="3"/>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
-        <v>3512500</v>
+        <v>3179900</v>
       </c>
       <c r="E48" s="3">
-        <v>3290500</v>
+        <v>3380500</v>
       </c>
       <c r="F48" s="3">
-        <v>3335800</v>
+        <v>3169200</v>
       </c>
       <c r="G48" s="3">
-        <v>3646900</v>
+        <v>3333800</v>
       </c>
       <c r="H48" s="3">
-        <v>3649300</v>
+        <v>3870300</v>
       </c>
       <c r="I48" s="3">
+        <v>4079700</v>
+      </c>
+      <c r="J48" s="3">
         <v>3534200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2974400</v>
       </c>
-      <c r="K48" s="3"/>
-    </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L48" s="3"/>
+    </row>
+    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
-        <v>822400</v>
+        <v>525500</v>
       </c>
       <c r="E49" s="3">
-        <v>846900</v>
+        <v>800700</v>
       </c>
       <c r="F49" s="3">
-        <v>734900</v>
+        <v>832400</v>
       </c>
       <c r="G49" s="3">
-        <v>726500</v>
+        <v>734500</v>
       </c>
       <c r="H49" s="3">
-        <v>735900</v>
+        <v>730900</v>
       </c>
       <c r="I49" s="3">
+        <v>734500</v>
+      </c>
+      <c r="J49" s="3">
         <v>774700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>355000</v>
       </c>
-      <c r="K49" s="3"/>
-    </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L49" s="3"/>
+    </row>
+    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -1737,9 +1850,12 @@
       <c r="J50" s="3">
         <v>0</v>
       </c>
-      <c r="K50" s="3"/>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K50" s="3">
+        <v>0</v>
+      </c>
+      <c r="L50" s="3"/>
+    </row>
+    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -1764,9 +1880,12 @@
       <c r="J51" s="3">
         <v>0</v>
       </c>
-      <c r="K51" s="3"/>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K51" s="3">
+        <v>0</v>
+      </c>
+      <c r="L51" s="3"/>
+    </row>
+    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
@@ -1791,9 +1910,12 @@
       <c r="J52" s="3">
         <v>0</v>
       </c>
-      <c r="K52" s="3"/>
-    </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K52" s="3">
+        <v>0</v>
+      </c>
+      <c r="L52" s="3"/>
+    </row>
+    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -1818,36 +1940,42 @@
       <c r="J53" s="3">
         <v>0</v>
       </c>
-      <c r="K53" s="3"/>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K53" s="3">
+        <v>0</v>
+      </c>
+      <c r="L53" s="3"/>
+    </row>
+    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
-        <v>8348400</v>
+        <v>7649400</v>
       </c>
       <c r="E54" s="3">
-        <v>8083700</v>
+        <v>8081000</v>
       </c>
       <c r="F54" s="3">
-        <v>8211900</v>
+        <v>7849700</v>
       </c>
       <c r="G54" s="3">
-        <v>8416300</v>
+        <v>8174200</v>
       </c>
       <c r="H54" s="3">
-        <v>8380000</v>
+        <v>8586000</v>
       </c>
       <c r="I54" s="3">
+        <v>8736800</v>
+      </c>
+      <c r="J54" s="3">
         <v>8361400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>7066600</v>
       </c>
-      <c r="K54" s="3"/>
-    </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L54" s="3"/>
+    </row>
+    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -1859,8 +1987,9 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+    </row>
+    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -1872,170 +2001,189 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+    </row>
+    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
-        <v>1119100</v>
+        <v>1090700</v>
       </c>
       <c r="E57" s="3">
-        <v>1108600</v>
+        <v>1187800</v>
       </c>
       <c r="F57" s="3">
-        <v>1253300</v>
+        <v>1177600</v>
       </c>
       <c r="G57" s="3">
-        <v>1227800</v>
+        <v>1343100</v>
       </c>
       <c r="H57" s="3">
-        <v>1227100</v>
+        <v>1318600</v>
       </c>
       <c r="I57" s="3">
+        <v>1325900</v>
+      </c>
+      <c r="J57" s="3">
         <v>1282000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1152200</v>
       </c>
-      <c r="K57" s="3"/>
-    </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L57" s="3"/>
+    </row>
+    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
-        <v>671200</v>
+        <v>1176800</v>
       </c>
       <c r="E58" s="3">
-        <v>602800</v>
+        <v>801900</v>
       </c>
       <c r="F58" s="3">
-        <v>662600</v>
+        <v>729100</v>
       </c>
       <c r="G58" s="3">
-        <v>637300</v>
+        <v>417700</v>
       </c>
       <c r="H58" s="3">
-        <v>557800</v>
+        <v>656200</v>
       </c>
       <c r="I58" s="3">
+        <v>620300</v>
+      </c>
+      <c r="J58" s="3">
         <v>1027600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>682400</v>
       </c>
-      <c r="K58" s="3"/>
-    </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L58" s="3"/>
+    </row>
+    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
-        <v>399000</v>
+        <v>401200</v>
       </c>
       <c r="E59" s="3">
-        <v>387500</v>
+        <v>354600</v>
       </c>
       <c r="F59" s="3">
-        <v>338600</v>
+        <v>350000</v>
       </c>
       <c r="G59" s="3">
-        <v>301100</v>
+        <v>685900</v>
       </c>
       <c r="H59" s="3">
-        <v>377200</v>
+        <v>280200</v>
       </c>
       <c r="I59" s="3">
+        <v>299700</v>
+      </c>
+      <c r="J59" s="3">
         <v>325100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>379100</v>
       </c>
-      <c r="K59" s="3"/>
-    </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L59" s="3"/>
+    </row>
+    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
-        <v>2189400</v>
+        <v>2668700</v>
       </c>
       <c r="E60" s="3">
-        <v>2099000</v>
+        <v>2344400</v>
       </c>
       <c r="F60" s="3">
-        <v>2254500</v>
+        <v>2256700</v>
       </c>
       <c r="G60" s="3">
-        <v>2166200</v>
+        <v>2446700</v>
       </c>
       <c r="H60" s="3">
-        <v>2162100</v>
+        <v>2255000</v>
       </c>
       <c r="I60" s="3">
+        <v>2245900</v>
+      </c>
+      <c r="J60" s="3">
         <v>2634700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2369100</v>
       </c>
-      <c r="K60" s="3"/>
-    </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L60" s="3"/>
+    </row>
+    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
-        <v>2277900</v>
+        <v>2066300</v>
       </c>
       <c r="E61" s="3">
-        <v>2327700</v>
+        <v>2310600</v>
       </c>
       <c r="F61" s="3">
-        <v>2272800</v>
+        <v>2331800</v>
       </c>
       <c r="G61" s="3">
-        <v>2440500</v>
+        <v>2389100</v>
       </c>
       <c r="H61" s="3">
-        <v>2496700</v>
+        <v>2638500</v>
       </c>
       <c r="I61" s="3">
+        <v>2861100</v>
+      </c>
+      <c r="J61" s="3">
         <v>2078700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1692400</v>
       </c>
-      <c r="K61" s="3"/>
-    </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L61" s="3"/>
+    </row>
+    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
-        <v>98400</v>
+        <v>215500</v>
       </c>
       <c r="E62" s="3">
-        <v>94800</v>
+        <v>233400</v>
       </c>
       <c r="F62" s="3">
-        <v>168300</v>
+        <v>220100</v>
       </c>
       <c r="G62" s="3">
-        <v>188300</v>
+        <v>341000</v>
       </c>
       <c r="H62" s="3">
-        <v>192000</v>
+        <v>339600</v>
       </c>
       <c r="I62" s="3">
+        <v>362600</v>
+      </c>
+      <c r="J62" s="3">
         <v>200200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>52800</v>
       </c>
-      <c r="K62" s="3"/>
-    </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L62" s="3"/>
+    </row>
+    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -2060,9 +2208,12 @@
       <c r="J63" s="3">
         <v>0</v>
       </c>
-      <c r="K63" s="3"/>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K63" s="3">
+        <v>0</v>
+      </c>
+      <c r="L63" s="3"/>
+    </row>
+    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -2087,9 +2238,12 @@
       <c r="J64" s="3">
         <v>0</v>
       </c>
-      <c r="K64" s="3"/>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K64" s="3">
+        <v>0</v>
+      </c>
+      <c r="L64" s="3"/>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -2114,36 +2268,42 @@
       <c r="J65" s="3">
         <v>0</v>
       </c>
-      <c r="K65" s="3"/>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K65" s="3">
+        <v>0</v>
+      </c>
+      <c r="L65" s="3"/>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
-        <v>4763300</v>
+        <v>5064700</v>
       </c>
       <c r="E66" s="3">
-        <v>4721900</v>
+        <v>5021000</v>
       </c>
       <c r="F66" s="3">
-        <v>4853300</v>
+        <v>4941300</v>
       </c>
       <c r="G66" s="3">
-        <v>4958900</v>
+        <v>5301500</v>
       </c>
       <c r="H66" s="3">
-        <v>5013000</v>
+        <v>5378900</v>
       </c>
       <c r="I66" s="3">
+        <v>5602500</v>
+      </c>
+      <c r="J66" s="3">
         <v>5091800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4280800</v>
       </c>
-      <c r="K66" s="3"/>
-    </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L66" s="3"/>
+    </row>
+    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -2155,8 +2315,9 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -2181,9 +2342,12 @@
       <c r="J68" s="3">
         <v>0</v>
       </c>
-      <c r="K68" s="3"/>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K68" s="3">
+        <v>0</v>
+      </c>
+      <c r="L68" s="3"/>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -2208,9 +2372,12 @@
       <c r="J69" s="3">
         <v>0</v>
       </c>
-      <c r="K69" s="3"/>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K69" s="3">
+        <v>0</v>
+      </c>
+      <c r="L69" s="3"/>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -2235,9 +2402,12 @@
       <c r="J70" s="3">
         <v>0</v>
       </c>
-      <c r="K70" s="3"/>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K70" s="3">
+        <v>0</v>
+      </c>
+      <c r="L70" s="3"/>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -2262,36 +2432,42 @@
       <c r="J71" s="3">
         <v>0</v>
       </c>
-      <c r="K71" s="3"/>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K71" s="3">
+        <v>0</v>
+      </c>
+      <c r="L71" s="3"/>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
-        <v>2469800</v>
+        <v>1342600</v>
       </c>
       <c r="E72" s="3">
-        <v>2215500</v>
+        <v>1940100</v>
       </c>
       <c r="F72" s="3">
-        <v>2284400</v>
+        <v>1748400</v>
       </c>
       <c r="G72" s="3">
-        <v>2265900</v>
+        <v>1805800</v>
       </c>
       <c r="H72" s="3">
-        <v>2213300</v>
+        <v>1995400</v>
       </c>
       <c r="I72" s="3">
+        <v>1933400</v>
+      </c>
+      <c r="J72" s="3">
         <v>2126900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2057700</v>
       </c>
-      <c r="K72" s="3"/>
-    </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L72" s="3"/>
+    </row>
+    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -2316,9 +2492,12 @@
       <c r="J73" s="3">
         <v>0</v>
       </c>
-      <c r="K73" s="3"/>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K73" s="3">
+        <v>0</v>
+      </c>
+      <c r="L73" s="3"/>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -2343,9 +2522,12 @@
       <c r="J74" s="3">
         <v>0</v>
       </c>
-      <c r="K74" s="3"/>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K74" s="3">
+        <v>0</v>
+      </c>
+      <c r="L74" s="3"/>
+    </row>
+    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -2370,36 +2552,42 @@
       <c r="J75" s="3">
         <v>0</v>
       </c>
-      <c r="K75" s="3"/>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K75" s="3">
+        <v>0</v>
+      </c>
+      <c r="L75" s="3"/>
+    </row>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
-        <v>3453400</v>
+        <v>2454200</v>
       </c>
       <c r="E76" s="3">
-        <v>3230000</v>
+        <v>2953100</v>
       </c>
       <c r="F76" s="3">
-        <v>3236400</v>
+        <v>2786800</v>
       </c>
       <c r="G76" s="3">
-        <v>3253900</v>
+        <v>2757400</v>
       </c>
       <c r="H76" s="3">
-        <v>3235100</v>
+        <v>3002900</v>
       </c>
       <c r="I76" s="3">
+        <v>2980700</v>
+      </c>
+      <c r="J76" s="3">
         <v>3085400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2631800</v>
       </c>
-      <c r="K76" s="3"/>
-    </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L76" s="3"/>
+    </row>
+    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -2424,68 +2612,77 @@
       <c r="J77" s="3">
         <v>0</v>
       </c>
-      <c r="K77" s="3"/>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K77" s="3">
+        <v>0</v>
+      </c>
+      <c r="L77" s="3"/>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44651</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44286</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43921</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43555</v>
       </c>
-      <c r="K80" s="2"/>
-    </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L80" s="2"/>
+    </row>
+    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
-        <v>327700</v>
+        <v>-402200</v>
       </c>
       <c r="E81" s="3">
-        <v>293300</v>
+        <v>266600</v>
       </c>
       <c r="F81" s="3">
-        <v>301900</v>
+        <v>242200</v>
       </c>
       <c r="G81" s="3">
-        <v>355900</v>
+        <v>69700</v>
       </c>
       <c r="H81" s="3">
-        <v>247400</v>
+        <v>343100</v>
       </c>
       <c r="I81" s="3">
+        <v>215700</v>
+      </c>
+      <c r="J81" s="3">
         <v>282800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>238900</v>
       </c>
-      <c r="K81" s="3"/>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L81" s="3"/>
+    </row>
+    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -2497,35 +2694,39 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+    </row>
+    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
-        <v>328800</v>
+        <v>358800</v>
       </c>
       <c r="E83" s="3">
-        <v>308000</v>
+        <v>321900</v>
       </c>
       <c r="F83" s="3">
-        <v>338400</v>
+        <v>300600</v>
       </c>
       <c r="G83" s="3">
-        <v>357200</v>
+        <v>342800</v>
       </c>
       <c r="H83" s="3">
-        <v>352900</v>
+        <v>362600</v>
       </c>
       <c r="I83" s="3">
+        <v>355600</v>
+      </c>
+      <c r="J83" s="3">
         <v>325200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>249300</v>
       </c>
-      <c r="K83" s="3"/>
-    </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L83" s="3"/>
+    </row>
+    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -2550,9 +2751,12 @@
       <c r="J84" s="3">
         <v>0</v>
       </c>
-      <c r="K84" s="3"/>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K84" s="3">
+        <v>0</v>
+      </c>
+      <c r="L84" s="3"/>
+    </row>
+    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -2577,9 +2781,12 @@
       <c r="J85" s="3">
         <v>0</v>
       </c>
-      <c r="K85" s="3"/>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K85" s="3">
+        <v>0</v>
+      </c>
+      <c r="L85" s="3"/>
+    </row>
+    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -2604,9 +2811,12 @@
       <c r="J86" s="3">
         <v>0</v>
       </c>
-      <c r="K86" s="3"/>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K86" s="3">
+        <v>0</v>
+      </c>
+      <c r="L86" s="3"/>
+    </row>
+    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -2631,9 +2841,12 @@
       <c r="J87" s="3">
         <v>0</v>
       </c>
-      <c r="K87" s="3"/>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K87" s="3">
+        <v>0</v>
+      </c>
+      <c r="L87" s="3"/>
+    </row>
+    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -2658,36 +2871,42 @@
       <c r="J88" s="3">
         <v>0</v>
       </c>
-      <c r="K88" s="3"/>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K88" s="3">
+        <v>0</v>
+      </c>
+      <c r="L88" s="3"/>
+    </row>
+    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
-        <v>622600</v>
+        <v>676600</v>
       </c>
       <c r="E89" s="3">
-        <v>526400</v>
+        <v>619300</v>
       </c>
       <c r="F89" s="3">
-        <v>428400</v>
+        <v>520400</v>
       </c>
       <c r="G89" s="3">
-        <v>589400</v>
+        <v>441300</v>
       </c>
       <c r="H89" s="3">
-        <v>692600</v>
+        <v>621400</v>
       </c>
       <c r="I89" s="3">
+        <v>743200</v>
+      </c>
+      <c r="J89" s="3">
         <v>406900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>511600</v>
       </c>
-      <c r="K89" s="3"/>
-    </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L89" s="3"/>
+    </row>
+    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -2699,35 +2918,39 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+    </row>
+    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
-        <v>-450600</v>
+        <v>-447700</v>
       </c>
       <c r="E91" s="3">
-        <v>-419600</v>
+        <v>-443800</v>
       </c>
       <c r="F91" s="3">
-        <v>-485600</v>
+        <v>-406400</v>
       </c>
       <c r="G91" s="3">
-        <v>-370400</v>
+        <v>-516700</v>
       </c>
       <c r="H91" s="3">
-        <v>-454900</v>
+        <v>-413700</v>
       </c>
       <c r="I91" s="3">
+        <v>-581600</v>
+      </c>
+      <c r="J91" s="3">
         <v>-574900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-624800</v>
       </c>
-      <c r="K91" s="3"/>
-    </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L91" s="3"/>
+    </row>
+    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -2752,9 +2975,12 @@
       <c r="J92" s="3">
         <v>0</v>
       </c>
-      <c r="K92" s="3"/>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K92" s="3">
+        <v>0</v>
+      </c>
+      <c r="L92" s="3"/>
+    </row>
+    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -2779,36 +3005,42 @@
       <c r="J93" s="3">
         <v>0</v>
       </c>
-      <c r="K93" s="3"/>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K93" s="3">
+        <v>0</v>
+      </c>
+      <c r="L93" s="3"/>
+    </row>
+    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
-        <v>-415100</v>
+        <v>-557300</v>
       </c>
       <c r="E94" s="3">
-        <v>-647700</v>
+        <v>-402500</v>
       </c>
       <c r="F94" s="3">
-        <v>-535100</v>
+        <v>-631300</v>
       </c>
       <c r="G94" s="3">
-        <v>-437700</v>
+        <v>-561200</v>
       </c>
       <c r="H94" s="3">
-        <v>-476500</v>
+        <v>-473800</v>
       </c>
       <c r="I94" s="3">
+        <v>-600300</v>
+      </c>
+      <c r="J94" s="3">
         <v>-1074300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-801400</v>
       </c>
-      <c r="K94" s="3"/>
-    </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L94" s="3"/>
+    </row>
+    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -2820,35 +3052,39 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+    </row>
+    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>116100</v>
       </c>
       <c r="E96" s="3">
-        <v>0</v>
+        <v>100900</v>
       </c>
       <c r="F96" s="3">
-        <v>0</v>
+        <v>93800</v>
       </c>
       <c r="G96" s="3">
-        <v>0</v>
+        <v>98100</v>
       </c>
       <c r="H96" s="3">
-        <v>0</v>
+        <v>92300</v>
       </c>
       <c r="I96" s="3">
-        <v>0</v>
+        <v>94600</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
-      </c>
-      <c r="K96" s="3"/>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+        <v>74600</v>
+      </c>
+      <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3"/>
+    </row>
+    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -2873,9 +3109,12 @@
       <c r="J97" s="3">
         <v>0</v>
       </c>
-      <c r="K97" s="3"/>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K97" s="3">
+        <v>0</v>
+      </c>
+      <c r="L97" s="3"/>
+    </row>
+    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -2900,9 +3139,12 @@
       <c r="J98" s="3">
         <v>0</v>
       </c>
-      <c r="K98" s="3"/>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K98" s="3">
+        <v>0</v>
+      </c>
+      <c r="L98" s="3"/>
+    </row>
+    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -2927,88 +3169,100 @@
       <c r="J99" s="3">
         <v>0</v>
       </c>
-      <c r="K99" s="3"/>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K99" s="3">
+        <v>0</v>
+      </c>
+      <c r="L99" s="3"/>
+    </row>
+    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
-        <v>-182500</v>
+        <v>-35900</v>
       </c>
       <c r="E100" s="3">
-        <v>97300</v>
+        <v>-188700</v>
       </c>
       <c r="F100" s="3">
-        <v>144900</v>
+        <v>83600</v>
       </c>
       <c r="G100" s="3">
-        <v>-54500</v>
+        <v>167900</v>
       </c>
       <c r="H100" s="3">
-        <v>-188900</v>
+        <v>-56000</v>
       </c>
       <c r="I100" s="3">
+        <v>-109600</v>
+      </c>
+      <c r="J100" s="3">
         <v>752600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>369100</v>
       </c>
-      <c r="K100" s="3"/>
-    </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L100" s="3"/>
+    </row>
+    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
-        <v>10900</v>
+        <v>4700</v>
       </c>
       <c r="E101" s="3">
-        <v>4400</v>
+        <v>10600</v>
       </c>
       <c r="F101" s="3">
-        <v>400</v>
+        <v>4900</v>
       </c>
       <c r="G101" s="3">
-        <v>6400</v>
+        <v>3400</v>
       </c>
       <c r="H101" s="3">
-        <v>900</v>
+        <v>11100</v>
       </c>
       <c r="I101" s="3">
+        <v>1600</v>
+      </c>
+      <c r="J101" s="3">
         <v>-6200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-2400</v>
       </c>
-      <c r="K101" s="3"/>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L101" s="3"/>
+    </row>
+    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
-        <v>35900</v>
+        <v>88100</v>
       </c>
       <c r="E102" s="3">
-        <v>-19500</v>
+        <v>38600</v>
       </c>
       <c r="F102" s="3">
-        <v>38500</v>
+        <v>-22400</v>
       </c>
       <c r="G102" s="3">
-        <v>103600</v>
+        <v>51400</v>
       </c>
       <c r="H102" s="3">
-        <v>28100</v>
+        <v>102700</v>
       </c>
       <c r="I102" s="3">
+        <v>34900</v>
+      </c>
+      <c r="J102" s="3">
         <v>79000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>76900</v>
       </c>
-      <c r="K102" s="3"/>
+      <c r="L102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
